--- a/media/shoblons/hospital/oth/otd_rep_d.xlsx
+++ b/media/shoblons/hospital/oth/otd_rep_d.xlsx
@@ -10,6 +10,9 @@
   <sheets>
     <sheet name="Лист1" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Titles" vbProcedure="false">Лист1!$7:$8</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -95,6 +98,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -166,7 +170,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -196,12 +200,13 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:L8"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="8.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="9.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="9.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="9.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="9.72"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -300,7 +305,7 @@
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
     </row>
-    <row r="8" customFormat="false" ht="36.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
